--- a/Template/TZ_glob.xlsx
+++ b/Template/TZ_glob.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code_and_Scripts_local\for_work\toir_raspredelenije_report\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CEB7A8-A2E0-4E84-BA80-50492A433B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A1B212-897E-4AD3-ABCA-6769436F9BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{87260E27-6010-4F4C-902C-0FBBD21A1BB8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{87260E27-6010-4F4C-902C-0FBBD21A1BB8}"/>
   </bookViews>
   <sheets>
     <sheet name="gen_cl" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3330" uniqueCount="521">
   <si>
     <t xml:space="preserve">Par. </t>
   </si>
@@ -1925,7 +1925,122 @@
     <cellStyle name="Финансовый [0] 2" xfId="3" xr:uid="{47616301-AC54-4CB6-89B3-D033E9758E4E}"/>
     <cellStyle name="Финансовый 2" xfId="5" xr:uid="{A7178EC7-4886-4E08-AB3B-462CE2DB2F85}"/>
   </cellStyles>
-  <dxfs count="56">
+  <dxfs count="31">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF2ECC71"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF2ECC71"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF2ECC71"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF2ECC71"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF2ECC71"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF2ECC71"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF2ECC71"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2308,13 +2423,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -2356,6 +2464,13 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -2391,347 +2506,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF2ECC71"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF2ECC71"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF2ECC71"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF2ECC71"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF2ECC71"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF2ECC71"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF2ECC71"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF2ECC71"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF2ECC71"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF2ECC71"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF2ECC71"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF2ECC71"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF2ECC71"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF2ECC71"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF2ECC71"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF2ECC71"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF2ECC71"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF2ECC71"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF2ECC71"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -2764,10 +2538,10 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Status (2)"/>
+      <sheetName val="Остаток"/>
       <sheetName val="Смотреть. Status CL"/>
       <sheetName val="Заполнять"/>
-      <sheetName val="folder_CS"/>
+      <sheetName val="folder_08_Check_lists"/>
       <sheetName val="TZ_glob"/>
       <sheetName val="Proect_TZ"/>
       <sheetName val="_"/>
@@ -2786,30 +2560,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D87E6C4-F18D-4F61-BB28-337D0C22ADCE}" name="Таблица33" displayName="Таблица33" ref="A1:M246" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D87E6C4-F18D-4F61-BB28-337D0C22ADCE}" name="Таблица33" displayName="Таблица33" ref="A1:M246" totalsRowShown="0" headerRowDxfId="30" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27" totalsRowBorderDxfId="26">
   <autoFilter ref="A1:M246" xr:uid="{6D87E6C4-F18D-4F61-BB28-337D0C22ADCE}"/>
   <tableColumns count="13">
-    <tableColumn id="5" xr3:uid="{171E931B-B3AC-4E04-B7B7-91B88450EA1C}" name="N" dataDxfId="12">
+    <tableColumn id="5" xr3:uid="{171E931B-B3AC-4E04-B7B7-91B88450EA1C}" name="N" dataDxfId="25">
       <calculatedColumnFormula>ROW()-ROW(Таблица33[[#Headers],[N]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{C258E592-3A0F-4F0C-9EBF-0779B80FF83B}" name="Par. " dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{F1A32094-FF59-4BA4-8310-2007A2E591D9}" name="Попис радова" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{518170FC-7304-4553-A330-E26E1C2C9ACF}" name="Перечень работ" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{74622D20-FBE4-49AB-B254-E4F8ED45F36B}" name="Периодичност" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{CC417EB5-37A1-4716-A266-BC7C1D22B581}" name="Podizvođač" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{856A9D2E-ACCA-454C-B164-F4F6FD6737E3}" name="Ukratko" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{5003DF01-D243-44DE-81C2-5A508BE6328C}" name="Reserved" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{69C99496-7F27-45EA-AEE2-C3A57D342D8E}" name="Comments" dataDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{25CA6553-BC37-4E41-A8ED-6C1248D7969B}" name="Столбец4" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{C258E592-3A0F-4F0C-9EBF-0779B80FF83B}" name="Par. " dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{F1A32094-FF59-4BA4-8310-2007A2E591D9}" name="Попис радова" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{518170FC-7304-4553-A330-E26E1C2C9ACF}" name="Перечень работ" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{74622D20-FBE4-49AB-B254-E4F8ED45F36B}" name="Периодичност" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{CC417EB5-37A1-4716-A266-BC7C1D22B581}" name="Podizvođač" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{856A9D2E-ACCA-454C-B164-F4F6FD6737E3}" name="Ukratko" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{5003DF01-D243-44DE-81C2-5A508BE6328C}" name="Reserved" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{69C99496-7F27-45EA-AEE2-C3A57D342D8E}" name="Comments" dataDxfId="17"/>
+    <tableColumn id="13" xr3:uid="{25CA6553-BC37-4E41-A8ED-6C1248D7969B}" name="Столбец4" dataDxfId="16">
       <calculatedColumnFormula>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Таблица33[[#This Row],[Par. ]],"а","a"),"б","b"),"в","v"),"г","g")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{84CC83F0-4E3F-4CA6-8000-79EF849F7AD3}" name="Столбец1" dataDxfId="2">
+    <tableColumn id="9" xr3:uid="{84CC83F0-4E3F-4CA6-8000-79EF849F7AD3}" name="Столбец1" dataDxfId="15">
       <calculatedColumnFormula>SUBSTITUTE(SUBSTITUTE(Таблица33[[#This Row],[Периодичност]],"Г","G"),"М","M")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{118CA49A-E119-49F5-B1EE-1C07261E6E94}" name="Столбец2" dataDxfId="1">
+    <tableColumn id="11" xr3:uid="{118CA49A-E119-49F5-B1EE-1C07261E6E94}" name="Столбец2" dataDxfId="14">
       <calculatedColumnFormula>_xlfn.TEXTJOIN("-",,Таблица33[[#This Row],[Столбец4]],Таблица33[[#This Row],[Reserved]],Таблица33[[#This Row],[Столбец1]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{2D39BA02-5228-4E0C-A73B-976D5BB74CAA}" name="Status CL" dataDxfId="0">
+    <tableColumn id="12" xr3:uid="{2D39BA02-5228-4E0C-A73B-976D5BB74CAA}" name="Status CL" dataDxfId="13">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3562,7 +3336,7 @@
       </c>
       <c r="M10" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -3606,7 +3380,7 @@
       </c>
       <c r="M11" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>На согласовании у GST</v>
+        <v>Согласован Заказчиком (code A)</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -3694,7 +3468,7 @@
       </c>
       <c r="M13" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>На согласовании у GST</v>
+        <v>Согласован Заказчиком (code A)</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -3914,7 +3688,7 @@
       </c>
       <c r="M18" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -4006,7 +3780,7 @@
       </c>
       <c r="M20" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -4050,7 +3824,7 @@
       </c>
       <c r="M21" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -4142,7 +3916,7 @@
       </c>
       <c r="M23" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -4450,7 +4224,7 @@
       </c>
       <c r="M30" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -4582,7 +4356,7 @@
       </c>
       <c r="M33" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -4670,7 +4444,7 @@
       </c>
       <c r="M35" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -4758,7 +4532,7 @@
       </c>
       <c r="M37" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -4866,11 +4640,11 @@
       <c r="E40" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>69</v>
+      <c r="F40" s="6">
+        <v>0</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="H40" s="19" t="s">
         <v>484</v>
@@ -5418,7 +5192,7 @@
       </c>
       <c r="M52" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
@@ -5902,7 +5676,7 @@
       </c>
       <c r="M63" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
@@ -6084,7 +5858,7 @@
       </c>
       <c r="M67" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>Согласован Заказчиком (code A)</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -6222,7 +5996,7 @@
       </c>
       <c r="M70" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>Согласован Заказчиком (code A)</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
@@ -6354,7 +6128,7 @@
       </c>
       <c r="M73" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
@@ -6442,7 +6216,7 @@
       </c>
       <c r="M75" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
@@ -6704,9 +6478,9 @@
         <f>_xlfn.TEXTJOIN("-",,Таблица33[[#This Row],[Столбец4]],Таблица33[[#This Row],[Reserved]],Таблица33[[#This Row],[Столбец1]])</f>
         <v>I.5.15-00-2M</v>
       </c>
-      <c r="M81" s="6" t="str">
-        <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Согласован Заказчиком (code A)</v>
+      <c r="M81" s="6" t="e">
+        <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -6748,9 +6522,9 @@
         <f>_xlfn.TEXTJOIN("-",,Таблица33[[#This Row],[Столбец4]],Таблица33[[#This Row],[Reserved]],Таблица33[[#This Row],[Столбец1]])</f>
         <v>I.5.15-00-6M</v>
       </c>
-      <c r="M82" s="6" t="str">
-        <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Согласован Заказчиком (code A)</v>
+      <c r="M82" s="6" t="e">
+        <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -6970,7 +6744,7 @@
       </c>
       <c r="M87" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>На согласовании у GST</v>
+        <v>Согласован Заказчиком (code A)</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -7014,7 +6788,7 @@
       </c>
       <c r="M88" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
@@ -7102,7 +6876,7 @@
       </c>
       <c r="M90" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -7190,7 +6964,7 @@
       </c>
       <c r="M92" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -7278,7 +7052,7 @@
       </c>
       <c r="M94" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -7320,9 +7094,9 @@
         <f>_xlfn.TEXTJOIN("-",,Таблица33[[#This Row],[Столбец4]],Таблица33[[#This Row],[Reserved]],Таблица33[[#This Row],[Столбец1]])</f>
         <v>I.6.9-00-1G</v>
       </c>
-      <c r="M95" s="6" t="str">
-        <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Согласован Заказчиком (code A)</v>
+      <c r="M95" s="6" t="e">
+        <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -7366,7 +7140,7 @@
       </c>
       <c r="M96" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="97" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -7718,7 +7492,7 @@
       </c>
       <c r="M104" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -7806,7 +7580,7 @@
       </c>
       <c r="M106" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>На согласовании у GST</v>
+        <v>Согласован Заказчиком (code A)</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -7894,7 +7668,7 @@
       </c>
       <c r="M108" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>На согласовании у GST</v>
+        <v>Согласован Заказчиком (code A)</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -8026,7 +7800,7 @@
       </c>
       <c r="M111" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>Согласован Заказчиком (code A)</v>
       </c>
     </row>
     <row r="112" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -9350,7 +9124,7 @@
       </c>
       <c r="M141" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="142" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -9394,7 +9168,7 @@
       </c>
       <c r="M142" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="143" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -9438,7 +9212,7 @@
       </c>
       <c r="M143" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
@@ -9482,7 +9256,7 @@
       </c>
       <c r="M144" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>На согласовании у GST</v>
+        <v>Согласован Заказчиком (code A)</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.25">
@@ -9526,7 +9300,7 @@
       </c>
       <c r="M145" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>На согласовании у GST</v>
+        <v>Согласован Заказчиком (code A)</v>
       </c>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.25">
@@ -9570,7 +9344,7 @@
       </c>
       <c r="M146" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>На согласовании у GST</v>
+        <v>Согласован Заказчиком (code A)</v>
       </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.25">
@@ -9614,7 +9388,7 @@
       </c>
       <c r="M147" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>На согласовании у GST</v>
+        <v>Согласован Заказчиком (code A)</v>
       </c>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.25">
@@ -9702,7 +9476,7 @@
       </c>
       <c r="M149" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>На согласовании у GST</v>
+        <v>Согласован Заказчиком (code A)</v>
       </c>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.25">
@@ -10230,7 +10004,7 @@
       </c>
       <c r="M161" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="162" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -10318,7 +10092,7 @@
       </c>
       <c r="M163" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>На согласовании у GST</v>
+        <v>Согласован Заказчиком (code A)</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -10362,7 +10136,7 @@
       </c>
       <c r="M164" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>На согласовании у GST</v>
+        <v>Согласован Заказчиком (code A)</v>
       </c>
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.25">
@@ -10716,7 +10490,7 @@
       </c>
       <c r="M172" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>На согласовании у GST</v>
+        <v>Согласован Заказчиком (code A)</v>
       </c>
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.25">
@@ -10760,7 +10534,7 @@
       </c>
       <c r="M173" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>На согласовании у GST</v>
+        <v>Согласован Заказчиком (code A)</v>
       </c>
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.25">
@@ -10804,7 +10578,7 @@
       </c>
       <c r="M174" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="175" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -10848,7 +10622,7 @@
       </c>
       <c r="M175" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="176" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -11160,7 +10934,7 @@
       </c>
       <c r="M182" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="183" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -11204,7 +10978,7 @@
       </c>
       <c r="M183" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="184" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -11380,7 +11154,7 @@
       </c>
       <c r="M187" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="188" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -11422,9 +11196,9 @@
         <f>_xlfn.TEXTJOIN("-",,Таблица33[[#This Row],[Столбец4]],Таблица33[[#This Row],[Reserved]],Таблица33[[#This Row],[Столбец1]])</f>
         <v>II.8.4-00-1G</v>
       </c>
-      <c r="M188" s="6" t="e">
-        <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>#N/A</v>
+      <c r="M188" s="6" t="str">
+        <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="189" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -11512,7 +11286,7 @@
       </c>
       <c r="M190" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="191" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -11558,7 +11332,7 @@
       </c>
       <c r="M191" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="192" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -11602,7 +11376,7 @@
       </c>
       <c r="M192" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="193" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -11646,7 +11420,7 @@
       </c>
       <c r="M193" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="194" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -11734,7 +11508,7 @@
       </c>
       <c r="M195" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="196" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -11998,7 +11772,7 @@
       </c>
       <c r="M201" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="202" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -12086,7 +11860,7 @@
       </c>
       <c r="M203" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="204" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -12130,7 +11904,7 @@
       </c>
       <c r="M204" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="205" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -12174,7 +11948,7 @@
       </c>
       <c r="M205" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.25">
@@ -12350,7 +12124,7 @@
       </c>
       <c r="M209" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>На согласовании у GST</v>
+        <v>Согласован Заказчиком (code A)</v>
       </c>
     </row>
     <row r="210" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -12702,7 +12476,7 @@
       </c>
       <c r="M217" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="218" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -12746,7 +12520,7 @@
       </c>
       <c r="M218" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="219" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -12966,7 +12740,7 @@
       </c>
       <c r="M223" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>На согласовании у GST</v>
+        <v>Согласован Заказчиком (code A)</v>
       </c>
     </row>
     <row r="224" spans="1:13" x14ac:dyDescent="0.25">
@@ -13054,7 +12828,7 @@
       </c>
       <c r="M225" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>На согласовании у GST</v>
+        <v>Согласован Заказчиком (code A)</v>
       </c>
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.25">
@@ -13098,7 +12872,7 @@
       </c>
       <c r="M226" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.25">
@@ -13236,7 +13010,7 @@
       </c>
       <c r="M229" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>На согласовании у GST</v>
+        <v>Согласован Заказчиком (code A)</v>
       </c>
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.25">
@@ -13282,7 +13056,7 @@
       </c>
       <c r="M230" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>На согласовании у GST</v>
+        <v>Согласован Заказчиком (code A)</v>
       </c>
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.25">
@@ -13328,7 +13102,7 @@
       </c>
       <c r="M231" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="232" spans="1:13" x14ac:dyDescent="0.25">
@@ -13374,7 +13148,7 @@
       </c>
       <c r="M232" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.25">
@@ -13462,7 +13236,7 @@
       </c>
       <c r="M234" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.25">
@@ -13506,7 +13280,7 @@
       </c>
       <c r="M235" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="236" spans="1:13" x14ac:dyDescent="0.25">
@@ -13594,7 +13368,7 @@
       </c>
       <c r="M237" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="238" spans="1:13" x14ac:dyDescent="0.25">
@@ -13812,9 +13586,9 @@
         <f>_xlfn.TEXTJOIN("-",,Таблица33[[#This Row],[Столбец4]],Таблица33[[#This Row],[Reserved]],Таблица33[[#This Row],[Столбец1]])</f>
         <v>II.26.3-00-1G</v>
       </c>
-      <c r="M242" s="6" t="e">
-        <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>#N/A</v>
+      <c r="M242" s="6" t="str">
+        <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="243" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -13900,7 +13674,7 @@
       </c>
       <c r="M244" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
     <row r="245" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -13988,67 +13762,67 @@
       </c>
       <c r="M246" s="6" t="str">
         <f>_xlfn.XLOOKUP(Таблица33[[#This Row],[Столбец2]],[1]!Status[InPrPer],[1]!Status[Status],,0,1)</f>
-        <v>Формируется для отправки в GST</v>
+        <v>На согласовании у GST</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="43" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B246">
-    <cfRule type="duplicateValues" dxfId="41" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C191">
-    <cfRule type="duplicateValues" dxfId="39" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C137:D137 C141:D142 C175:D175 C192:D193 C199:D200 C213:D213 C241:D242 C243 C244:D244">
-    <cfRule type="expression" dxfId="37" priority="10">
+    <cfRule type="expression" dxfId="9" priority="10">
       <formula>C137&lt;&gt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C152:E164">
-    <cfRule type="expression" dxfId="35" priority="9">
+    <cfRule type="expression" dxfId="8" priority="9">
       <formula>C152&lt;&gt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E27 E29 E32 E36 E38 E43 E45 E51 E54 E56 E62 E71 E74 E77 E79 E81 E86 E89 E91 E93 E102 E122 E124 E129 E192 E194:E195 E197 E199 E206:E207 E215 E225 E233 E235:E236 E238">
-    <cfRule type="expression" dxfId="33" priority="8">
+    <cfRule type="expression" dxfId="7" priority="8">
       <formula>$E28=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47:E48 E58:E59 E98:E99 E229">
-    <cfRule type="expression" dxfId="31" priority="9">
+    <cfRule type="expression" dxfId="6" priority="14">
       <formula>$E49=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E65 E112 E230">
-    <cfRule type="expression" dxfId="29" priority="10">
+    <cfRule type="expression" dxfId="5" priority="15">
       <formula>$E68=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E66:E67">
-    <cfRule type="expression" dxfId="27" priority="12">
+    <cfRule type="expression" dxfId="4" priority="16">
       <formula>$E71=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E113">
-    <cfRule type="expression" dxfId="25" priority="13">
+    <cfRule type="expression" dxfId="3" priority="17">
       <formula>$E117=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E114:E115">
-    <cfRule type="expression" dxfId="23" priority="11">
+    <cfRule type="expression" dxfId="2" priority="18">
       <formula>$E120=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E130:E191 E2:E26 E28 E30:E31 E33:E35 E37 E39:E42 E44 E46 E49:E50 E52:E53 E55 E57 E60:E61 E63:E64 E68:E70 E72:E73 E75:E76 E78 E80 E82:E85 E87:E88 E90 E92 E94:E97 E100:E101 E103:E111 E116:E121 E123 E125:E128 E193 E196 E198 E200:E205 E208:E214 E216:E224 E226:E228 E231:E232 E234:E237 E239:E246">
-    <cfRule type="expression" dxfId="21" priority="6">
+    <cfRule type="expression" dxfId="1" priority="6">
       <formula>#REF!=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E141:E142">
-    <cfRule type="expression" dxfId="19" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>E141&lt;&gt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14249,15 +14023,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="691b8695-a47c-478e-9925-ebd689fbd75e" xsi:nil="true"/>
@@ -14266,6 +14031,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14288,14 +14062,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{052CAC44-A069-4A8A-8F22-17B240C9B761}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{380CB200-3391-4A8E-A209-D63C4F6B47D0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -14310,4 +14076,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{052CAC44-A069-4A8A-8F22-17B240C9B761}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>